--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3745,6 +3745,117 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120506326</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Järvdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>431244</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7004249</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -3849,7 +3849,7 @@
         <v>120752197</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -3849,7 +3849,7 @@
         <v>120752197</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -3849,7 +3849,7 @@
         <v>120752197</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 47913-2023 artfynd.xlsx
+++ b/artfynd/A 47913-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104305748</v>
+        <v>120506326</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
+        <v>57348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,11 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431243.8687340269</v>
+        <v>431244</v>
       </c>
       <c r="R5" t="n">
-        <v>7004249.923676839</v>
+        <v>7004249</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1110,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -3735,10 +3726,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120506326</v>
+        <v>120752197</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3751,41 +3742,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järvdalen, Jmt</t>
+          <t>MD41:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431244</v>
+        <v>431247</v>
       </c>
       <c r="R30" t="n">
-        <v>7004249</v>
+        <v>7004205</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3809,17 +3796,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,127 +3826,15 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>120752197</v>
-      </c>
-      <c r="B31" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>MD41:Åre, SE-JA, SE, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>431247</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7004205</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Mörsil</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
